--- a/business_surveys/045_library_organization_structure_survey--business_surveys.xlsx
+++ b/business_surveys/045_library_organization_structure_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -785,8 +785,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -814,12 +814,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'flat',_'label':_'flat'}</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'flat', 'label': 'Flat'}</t>
+          <t>Flat</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'hierarchical',_'label':_'hierarchical'}</t>
+          <t>hierarchical</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'hierarchical', 'label': 'Hierarchical'}</t>
+          <t>Hierarchical</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'librarian',_'label':_'librarian'}</t>
+          <t>librarian</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'librarian', 'label': 'Librarian'}</t>
+          <t>Librarian</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'technical',_'label':_'technical'}</t>
+          <t>technical</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'technical', 'label': 'Technical'}</t>
+          <t>Technical</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'support_staff',_'label':_'support_staff'}</t>
+          <t>support_staff</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'support_staff', 'label': 'Support Staff'}</t>
+          <t>Support Staff</t>
         </is>
       </c>
     </row>
